--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121628270</v>
+        <v>121628271</v>
       </c>
       <c r="B2" t="n">
-        <v>58221</v>
+        <v>58185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,9 +718,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517110</v>
+        <v>517132</v>
       </c>
       <c r="R2" t="n">
-        <v>6575055</v>
+        <v>6575060</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121628271</v>
+        <v>121628270</v>
       </c>
       <c r="B3" t="n">
-        <v>58185</v>
+        <v>58221</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,9 +839,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517132</v>
+        <v>517110</v>
       </c>
       <c r="R3" t="n">
-        <v>6575060</v>
+        <v>6575055</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121628271</v>
       </c>
       <c r="B2" t="n">
-        <v>58185</v>
+        <v>58188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121628270</v>
       </c>
       <c r="B3" t="n">
-        <v>58221</v>
+        <v>58224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121628271</v>
+        <v>121628270</v>
       </c>
       <c r="B2" t="n">
-        <v>58188</v>
+        <v>58224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,9 +718,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517132</v>
+        <v>517110</v>
       </c>
       <c r="R2" t="n">
-        <v>6575060</v>
+        <v>6575055</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121628270</v>
+        <v>121628271</v>
       </c>
       <c r="B3" t="n">
-        <v>58224</v>
+        <v>58188</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,9 +839,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517110</v>
+        <v>517132</v>
       </c>
       <c r="R3" t="n">
-        <v>6575055</v>
+        <v>6575060</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121628270</v>
+        <v>121628271</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,9 +718,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517110</v>
+        <v>517132</v>
       </c>
       <c r="R2" t="n">
-        <v>6575055</v>
+        <v>6575060</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121628271</v>
+        <v>121628270</v>
       </c>
       <c r="B3" t="n">
-        <v>58188</v>
+        <v>58224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,9 +839,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517132</v>
+        <v>517110</v>
       </c>
       <c r="R3" t="n">
-        <v>6575060</v>
+        <v>6575055</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121628270</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>121628271</v>
       </c>
       <c r="B3" t="n">
-        <v>58188</v>
+        <v>58196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 45311-2019 artfynd.xlsx
+++ b/artfynd/A 45311-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121628270</v>
+        <v>121628271</v>
       </c>
       <c r="B2" t="n">
-        <v>58232</v>
+        <v>58196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208242</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -718,9 +718,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517110</v>
+        <v>517132</v>
       </c>
       <c r="R2" t="n">
-        <v>6575055</v>
+        <v>6575060</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121628271</v>
+        <v>121628270</v>
       </c>
       <c r="B3" t="n">
-        <v>58196</v>
+        <v>58232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,9 +839,9 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517132</v>
+        <v>517110</v>
       </c>
       <c r="R3" t="n">
-        <v>6575060</v>
+        <v>6575055</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
